--- a/Result/profitability/4169.xlsx
+++ b/Result/profitability/4169.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM37"/>
+  <dimension ref="A1:AM38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.64</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07124999999999999</v>
+        <v>-0.11625</v>
       </c>
       <c r="N2" t="n">
-        <v>45.44875</v>
+        <v>45.35375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.04999999999999999</v>
+        <v>-0.06125</v>
       </c>
       <c r="N3" t="n">
-        <v>44.57125</v>
+        <v>44.5625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -5129,6 +5129,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4169</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>181</v>
+      </c>
+      <c r="D38" t="n">
+        <v>96</v>
+      </c>
+      <c r="E38" t="n">
+        <v>85</v>
+      </c>
+      <c r="F38" t="n">
+        <v>47.11</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-5.81%</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-9</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-0.007499999999999996</v>
+      </c>
+      <c r="N38" t="n">
+        <v>46.50625</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="X38" t="n">
+        <v>-0.711111111111111</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.460000000000001</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.05509518477043684</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>-1.8125</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.1899999999999977</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.004049445865302648</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK38" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
